--- a/output/pdf_financials_xlsx/NVT.xlsx
+++ b/output/pdf_financials_xlsx/NVT.xlsx
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.733545</v>
+        <v>-0.733545</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>-0.327436</v>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.2883</v>
+        <v>-5.325744</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.829464</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-3.276116</v>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2.518722</v>
+        <v>-2.518722</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.914732</v>
+        <v>-2.914732</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.638058</v>
+        <v>-1.638058</v>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.733545</v>
+        <v>-0.733545</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>-0.327436</v>
@@ -1803,13 +1803,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.518722</v>
+        <v>-2.518722</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.914732</v>
+        <v>-2.914732</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.638058</v>
+        <v>-1.638058</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.108129</v>
@@ -1842,7 +1842,7 @@
         <v>0.139155</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.733545</v>
+        <v>-0.733545</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>-0.327436</v>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>62.96805</v>
+        <v>-62.96805</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>97.15773299999999</v>
+        <v>-97.15773299999999</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>36.67725</v>
+        <v>-36.67725</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.733545</v>
+        <v>-0.733545</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.327436</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.733545</v>
+        <v>-0.733545</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.327436</v>
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10.27067119530948</v>
+        <v>189.7293288046905</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>-0</v>
@@ -6091,40 +6091,40 @@
         <v>4.307994</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.307994</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.205004</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.307994</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.317407</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.532013</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>4.540351</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>4.350497</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.350497</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.298759</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.427823</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.433521</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.503304</v>
       </c>
     </row>
     <row r="93">
@@ -9640,7 +9640,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -10757,7 +10761,11 @@
           <t>Reserves 7, 8</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11420,7 +11428,11 @@
           <t>Reserves 7, 8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -12747,7 +12759,11 @@
           <t>Reserves 7, 8 4,298,759</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -14365,7 +14381,11 @@
           <t>Reserves 6, 7</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -14975,7 +14995,11 @@
           <t>Reserves 7,8</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -15488,7 +15512,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -52692,10 +52720,10 @@
         </is>
       </c>
       <c r="R438" s="5" t="n">
-        <v>0.733545</v>
+        <v>-0.733545</v>
       </c>
       <c r="S438" s="5" t="n">
-        <v>0.327436</v>
+        <v>-0.327436</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -52779,10 +52807,10 @@
         </is>
       </c>
       <c r="R439" s="5" t="n">
-        <v>0.788807</v>
+        <v>-0.788807</v>
       </c>
       <c r="S439" s="5" t="n">
-        <v>0.347041</v>
+        <v>-0.347041</v>
       </c>
       <c r="T439" t="inlineStr">
         <is>
@@ -77025,13 +77053,13 @@
         </is>
       </c>
       <c r="E682" s="5" t="n">
-        <v>2.518722</v>
+        <v>-2.518722</v>
       </c>
       <c r="F682" s="5" t="n">
-        <v>2.914732</v>
+        <v>-2.914732</v>
       </c>
       <c r="G682" s="5" t="n">
-        <v>1.638058</v>
+        <v>-1.638058</v>
       </c>
       <c r="H682" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NVT.xlsx
+++ b/output/pdf_financials_xlsx/NVT.xlsx
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.06465899999999999</v>
+        <v>1.185337</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.04392</v>
+        <v>0.558404</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>0.048457</v>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.06465899999999999</v>
+        <v>-1.185337</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.04392</v>
+        <v>-0.558404</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>-0.048457</v>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.046359</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003062</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0005910000000000001</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.022364</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.006366</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002072</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.807022</v>
+        <v>2.853381</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.914732</v>
+        <v>2.917794</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.638058</v>
+        <v>1.638649</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.077119</v>
+        <v>-6.099483</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.666083</v>
+        <v>-0.672449</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.837446</v>
+        <v>-1.839518</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.845278</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.807022</v>
+        <v>2.853381</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.914732</v>
+        <v>2.917794</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.668072</v>
+        <v>1.668663</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.061706</v>
+        <v>-6.08407</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.646001</v>
+        <v>-0.652367</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.831275</v>
+        <v>-1.833347</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.845278</v>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.049948</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.023399</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.023399</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.841027</v>
@@ -2521,40 +2521,40 @@
         <v>0.129104</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.250264</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.022051</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.011192</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.587944</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.142189</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.007575</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.005175</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.0587</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.557438</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.115322</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.406408</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.321255</v>
       </c>
     </row>
     <row r="35">
@@ -2622,13 +2622,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.449948</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.023399</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.023399</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>2.349556</v>
@@ -2637,40 +2637,40 @@
         <v>1.701758</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.311555</v>
+        <v>0.561819</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.042051</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.02</v>
+        <v>0.031192</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.228927</v>
+        <v>0.816871</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.252362</v>
+        <v>0.394551</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.007575</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.005175</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.0587</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.557438</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.115322</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.406408</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.321255</v>
       </c>
     </row>
     <row r="37">
@@ -3321,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.08780399999999999</v>
+        <v>0.064405</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.146955</v>
+        <v>0.123556</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.559561</v>
@@ -3339,34 +3339,34 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.011192</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.591929</v>
+        <v>0.003985</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.161964</v>
+        <v>0.019775</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.009525</v>
+        <v>0.00195</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.008935</v>
+        <v>0.00376</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.09596</v>
+        <v>0.03726</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.725552</v>
+        <v>0.168114</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.283907</v>
+        <v>0.168585</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.410368</v>
+        <v>0.00396</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.323895</v>
+        <v>0.00264</v>
       </c>
     </row>
     <row r="49">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -52245,7 +52245,7 @@
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -58798,7 +58798,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -70738,7 +70738,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -76643,7 +76643,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E678" s="5" t="n">

--- a/output/pdf_financials_xlsx/NVT.xlsx
+++ b/output/pdf_financials_xlsx/NVT.xlsx
@@ -1371,7 +1371,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-5.325744</v>
+        <v>0.2883</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-5.829464</v>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>189.7293288046905</v>
+        <v>10.27067119530948</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>200</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.240472</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>0.187058</v>
       </c>
       <c r="Q64" s="3" t="n">
         <v>0</v>
@@ -4567,16 +4567,16 @@
         <v>0</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.046693</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.043031</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.0435</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.043075</v>
       </c>
     </row>
     <row r="68">
@@ -7167,16 +7167,16 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.008501999999999999</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005804</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010195</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004433</v>
       </c>
       <c r="H111" s="3" t="n">
         <v>0</v>
@@ -7417,13 +7417,13 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.172265</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.287239</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.176826</v>
       </c>
       <c r="M115" s="3" t="n">
         <v>0</v>
@@ -8547,16 +8547,16 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.008501999999999999</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005804</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010195</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004433</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
@@ -8607,7 +8607,7 @@
         <v>-1.158088</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.256966</v>
+        <v>-1.265468</v>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
@@ -8615,10 +8615,10 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.97029</v>
+        <v>-0.9804850000000001</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-0.877564</v>
+        <v>-0.881997</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>-0.209883</v>
@@ -29261,7 +29261,11 @@
           <t>Gross proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -29976,7 +29980,11 @@
           <t>Fair value of warrants issued with private placement</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -30386,7 +30394,11 @@
           <t>Net proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -31873,7 +31885,11 @@
           <t>Fair value of warrants issued with private placement $</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -32257,7 +32273,11 @@
           <t>Net proceeds from shares issuance</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33681,7 +33701,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -35507,7 +35531,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -38521,7 +38549,11 @@
           <t>Proceeds from shares issuance</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
           <t>-</t>
@@ -40753,7 +40785,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
@@ -42288,7 +42324,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -43817,7 +43857,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
@@ -45433,7 +45477,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -47740,7 +47788,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E389" s="5" t="n">
         <v>-0.2883</v>
       </c>
@@ -78148,7 +78200,11 @@
           <t>Future income tax (recovery) (Note 12a)</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr"/>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E693" s="5" t="n">
         <v>-0.2883</v>
       </c>
